--- a/assets/Excells/CotisationSpeciale0.xlsx
+++ b/assets/Excells/CotisationSpeciale0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwamutalamiantezila/Documents/LukalaPhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668F449A-0714-D84B-B912-88477CC514E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE96D20-BA2C-8741-B50A-FD630FEF5086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="8160" windowWidth="35900" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
+    <workbookView xWindow="-1480" yWindow="680" windowWidth="34140" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="75">
   <si>
     <t>Eugenie Malayi</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>René Mamingi</t>
+  </si>
+  <si>
+    <t>Juille</t>
   </si>
 </sst>
 </file>
@@ -543,6 +546,7 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -552,7 +556,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF6F12D5-1178-994A-98D1-482C6B1D858E}">
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -901,12 +904,12 @@
     <col min="9" max="9" width="13.5" style="23" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" style="23" customWidth="1"/>
     <col min="11" max="11" width="15" style="23" customWidth="1"/>
-    <col min="12" max="19" width="13.1640625" style="23" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="25" width="13.1640625" style="23" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="27" max="27" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="28" customFormat="1" ht="77" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="77" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>9</v>
       </c>
@@ -964,16 +967,34 @@
       <c r="S1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="T1" s="38"/>
-    </row>
-    <row r="2" spans="1:21" s="28" customFormat="1" ht="31" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T1" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y1" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z1" s="38"/>
+    </row>
+    <row r="2" spans="1:27" s="28" customFormat="1" ht="31" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="48"/>
       <c r="F2" s="31"/>
       <c r="G2" s="15" t="s">
         <v>14</v>
@@ -1014,9 +1035,27 @@
       <c r="S2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="39"/>
-    </row>
-    <row r="3" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="39"/>
+    </row>
+    <row r="3" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1072,9 +1111,27 @@
       <c r="S3" s="9">
         <v>0</v>
       </c>
-      <c r="T3" s="40"/>
-    </row>
-    <row r="4" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T3" s="9">
+        <v>0</v>
+      </c>
+      <c r="U3" s="9">
+        <v>0</v>
+      </c>
+      <c r="V3" s="9">
+        <v>0</v>
+      </c>
+      <c r="W3" s="9">
+        <v>0</v>
+      </c>
+      <c r="X3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="40"/>
+    </row>
+    <row r="4" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -1130,9 +1187,27 @@
       <c r="S4" s="9">
         <v>0</v>
       </c>
-      <c r="T4" s="40"/>
-    </row>
-    <row r="5" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T4" s="9">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="40"/>
+    </row>
+    <row r="5" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
@@ -1188,9 +1263,27 @@
       <c r="S5" s="9">
         <v>10</v>
       </c>
-      <c r="T5" s="40"/>
-    </row>
-    <row r="6" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="40"/>
+    </row>
+    <row r="6" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -1246,9 +1339,27 @@
       <c r="S6" s="9">
         <v>0</v>
       </c>
-      <c r="T6" s="40"/>
-    </row>
-    <row r="7" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T6" s="9">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="40"/>
+    </row>
+    <row r="7" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -1304,9 +1415,27 @@
       <c r="S7" s="9">
         <v>0</v>
       </c>
-      <c r="T7" s="40"/>
-    </row>
-    <row r="8" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T7" s="9">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="40"/>
+    </row>
+    <row r="8" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>19</v>
       </c>
@@ -1362,9 +1491,27 @@
       <c r="S8" s="9">
         <v>0</v>
       </c>
-      <c r="T8" s="40"/>
-    </row>
-    <row r="9" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="40"/>
+    </row>
+    <row r="9" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
@@ -1420,9 +1567,27 @@
       <c r="S9" s="9">
         <v>0</v>
       </c>
-      <c r="T9" s="40"/>
-    </row>
-    <row r="10" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="40"/>
+    </row>
+    <row r="10" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -1478,9 +1643,27 @@
       <c r="S10" s="9">
         <v>0</v>
       </c>
-      <c r="T10" s="40"/>
-    </row>
-    <row r="11" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="40"/>
+    </row>
+    <row r="11" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>39</v>
       </c>
@@ -1536,9 +1719,27 @@
       <c r="S11" s="9">
         <v>0</v>
       </c>
-      <c r="T11" s="40"/>
-    </row>
-    <row r="12" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="40"/>
+    </row>
+    <row r="12" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>60</v>
       </c>
@@ -1594,9 +1795,27 @@
       <c r="S12" s="9">
         <v>0</v>
       </c>
-      <c r="T12" s="40"/>
-    </row>
-    <row r="13" spans="1:21" s="3" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="40"/>
+    </row>
+    <row r="13" spans="1:27" s="3" customFormat="1" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
@@ -1667,13 +1886,37 @@
         <f>SUM(S3:S12)</f>
         <v>10</v>
       </c>
-      <c r="T13" s="42">
-        <f>SUM(D13:S13)</f>
+      <c r="T13" s="29">
+        <f t="shared" ref="T13:U13" si="1">SUM(T3:T12)</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="29">
+        <f>SUM(V3:V12)</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="29">
+        <f t="shared" ref="W13" si="2">SUM(W3:W12)</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="29">
+        <f>SUM(X3:X12)</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="29">
+        <f>SUM(Y3:Y12)</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="42">
+        <f>SUM(D13:Y13)</f>
         <v>1140</v>
       </c>
-      <c r="U13" s="48"/>
-    </row>
-    <row r="14" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AA13" s="45"/>
+    </row>
+    <row r="14" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="8"/>
@@ -1723,9 +1966,27 @@
       <c r="S14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T14" s="40"/>
-    </row>
-    <row r="15" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z14" s="40"/>
+    </row>
+    <row r="15" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="8"/>
@@ -1775,16 +2036,34 @@
       <c r="S15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T15" s="40"/>
-    </row>
-    <row r="16" spans="1:21" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z15" s="40"/>
+    </row>
+    <row r="16" spans="1:27" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="48"/>
       <c r="F16" s="31"/>
       <c r="G16" s="15" t="s">
         <v>14</v>
@@ -1825,9 +2104,27 @@
       <c r="S16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T16" s="40"/>
-    </row>
-    <row r="17" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z16" s="40"/>
+    </row>
+    <row r="17" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>4</v>
       </c>
@@ -1883,10 +2180,28 @@
       <c r="S17" s="44">
         <v>0</v>
       </c>
-      <c r="T17" s="40"/>
-      <c r="V17" s="6"/>
-    </row>
-    <row r="18" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T17" s="44">
+        <v>0</v>
+      </c>
+      <c r="U17" s="44">
+        <v>0</v>
+      </c>
+      <c r="V17" s="44">
+        <v>0</v>
+      </c>
+      <c r="W17" s="44">
+        <v>0</v>
+      </c>
+      <c r="X17" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="40"/>
+      <c r="AB17" s="6"/>
+    </row>
+    <row r="18" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>24</v>
       </c>
@@ -1942,10 +2257,28 @@
       <c r="S18" s="44">
         <v>0</v>
       </c>
-      <c r="T18" s="40"/>
-      <c r="V18" s="6"/>
-    </row>
-    <row r="19" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T18" s="44">
+        <v>0</v>
+      </c>
+      <c r="U18" s="44">
+        <v>0</v>
+      </c>
+      <c r="V18" s="44">
+        <v>0</v>
+      </c>
+      <c r="W18" s="44">
+        <v>0</v>
+      </c>
+      <c r="X18" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="40"/>
+      <c r="AB18" s="6"/>
+    </row>
+    <row r="19" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
@@ -2001,10 +2334,28 @@
       <c r="S19" s="44">
         <v>0</v>
       </c>
-      <c r="T19" s="40"/>
-      <c r="V19" s="6"/>
-    </row>
-    <row r="20" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T19" s="44">
+        <v>0</v>
+      </c>
+      <c r="U19" s="44">
+        <v>0</v>
+      </c>
+      <c r="V19" s="44">
+        <v>0</v>
+      </c>
+      <c r="W19" s="44">
+        <v>0</v>
+      </c>
+      <c r="X19" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="40"/>
+      <c r="AB19" s="6"/>
+    </row>
+    <row r="20" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>18</v>
       </c>
@@ -2060,10 +2411,28 @@
       <c r="S20" s="44">
         <v>0</v>
       </c>
-      <c r="T20" s="40"/>
-      <c r="V20" s="6"/>
-    </row>
-    <row r="21" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T20" s="44">
+        <v>0</v>
+      </c>
+      <c r="U20" s="44">
+        <v>0</v>
+      </c>
+      <c r="V20" s="44">
+        <v>0</v>
+      </c>
+      <c r="W20" s="44">
+        <v>0</v>
+      </c>
+      <c r="X20" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="40"/>
+      <c r="AB20" s="6"/>
+    </row>
+    <row r="21" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -2119,10 +2488,28 @@
       <c r="S21" s="44">
         <v>0</v>
       </c>
-      <c r="T21" s="40"/>
-      <c r="V21" s="6"/>
-    </row>
-    <row r="22" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T21" s="44">
+        <v>0</v>
+      </c>
+      <c r="U21" s="44">
+        <v>0</v>
+      </c>
+      <c r="V21" s="44">
+        <v>0</v>
+      </c>
+      <c r="W21" s="44">
+        <v>0</v>
+      </c>
+      <c r="X21" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="40"/>
+      <c r="AB21" s="6"/>
+    </row>
+    <row r="22" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>25</v>
       </c>
@@ -2178,10 +2565,28 @@
       <c r="S22" s="44">
         <v>0</v>
       </c>
-      <c r="T22" s="40"/>
-      <c r="V22" s="6"/>
-    </row>
-    <row r="23" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T22" s="44">
+        <v>0</v>
+      </c>
+      <c r="U22" s="44">
+        <v>0</v>
+      </c>
+      <c r="V22" s="44">
+        <v>0</v>
+      </c>
+      <c r="W22" s="44">
+        <v>0</v>
+      </c>
+      <c r="X22" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="40"/>
+      <c r="AB22" s="6"/>
+    </row>
+    <row r="23" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>28</v>
       </c>
@@ -2237,10 +2642,28 @@
       <c r="S23" s="44">
         <v>0</v>
       </c>
-      <c r="T23" s="40"/>
-      <c r="V23" s="6"/>
-    </row>
-    <row r="24" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T23" s="44">
+        <v>0</v>
+      </c>
+      <c r="U23" s="44">
+        <v>0</v>
+      </c>
+      <c r="V23" s="44">
+        <v>0</v>
+      </c>
+      <c r="W23" s="44">
+        <v>0</v>
+      </c>
+      <c r="X23" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="40"/>
+      <c r="AB23" s="6"/>
+    </row>
+    <row r="24" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>47</v>
       </c>
@@ -2296,10 +2719,28 @@
       <c r="S24" s="44">
         <v>0</v>
       </c>
-      <c r="T24" s="40"/>
-      <c r="V24" s="6"/>
-    </row>
-    <row r="25" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T24" s="44">
+        <v>0</v>
+      </c>
+      <c r="U24" s="44">
+        <v>0</v>
+      </c>
+      <c r="V24" s="44">
+        <v>0</v>
+      </c>
+      <c r="W24" s="44">
+        <v>0</v>
+      </c>
+      <c r="X24" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="40"/>
+      <c r="AB24" s="6"/>
+    </row>
+    <row r="25" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>27</v>
       </c>
@@ -2355,10 +2796,28 @@
       <c r="S25" s="44">
         <v>0</v>
       </c>
-      <c r="T25" s="40"/>
-      <c r="V25" s="6"/>
-    </row>
-    <row r="26" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T25" s="44">
+        <v>0</v>
+      </c>
+      <c r="U25" s="44">
+        <v>0</v>
+      </c>
+      <c r="V25" s="44">
+        <v>0</v>
+      </c>
+      <c r="W25" s="44">
+        <v>0</v>
+      </c>
+      <c r="X25" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="40"/>
+      <c r="AB25" s="6"/>
+    </row>
+    <row r="26" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>30</v>
       </c>
@@ -2414,10 +2873,28 @@
       <c r="S26" s="44">
         <v>0</v>
       </c>
-      <c r="T26" s="40"/>
-      <c r="V26" s="6"/>
-    </row>
-    <row r="27" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T26" s="44">
+        <v>0</v>
+      </c>
+      <c r="U26" s="44">
+        <v>0</v>
+      </c>
+      <c r="V26" s="44">
+        <v>0</v>
+      </c>
+      <c r="W26" s="44">
+        <v>0</v>
+      </c>
+      <c r="X26" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="40"/>
+      <c r="AB26" s="6"/>
+    </row>
+    <row r="27" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>22</v>
       </c>
@@ -2473,10 +2950,28 @@
       <c r="S27" s="44">
         <v>0</v>
       </c>
-      <c r="T27" s="40"/>
-      <c r="V27" s="6"/>
-    </row>
-    <row r="28" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T27" s="44">
+        <v>0</v>
+      </c>
+      <c r="U27" s="44">
+        <v>0</v>
+      </c>
+      <c r="V27" s="44">
+        <v>0</v>
+      </c>
+      <c r="W27" s="44">
+        <v>0</v>
+      </c>
+      <c r="X27" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="40"/>
+      <c r="AB27" s="6"/>
+    </row>
+    <row r="28" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>35</v>
       </c>
@@ -2532,10 +3027,28 @@
       <c r="S28" s="16">
         <v>0</v>
       </c>
-      <c r="T28" s="40"/>
-      <c r="V28" s="6"/>
-    </row>
-    <row r="29" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T28" s="44">
+        <v>0</v>
+      </c>
+      <c r="U28" s="44">
+        <v>0</v>
+      </c>
+      <c r="V28" s="44">
+        <v>0</v>
+      </c>
+      <c r="W28" s="44">
+        <v>0</v>
+      </c>
+      <c r="X28" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="40"/>
+      <c r="AB28" s="6"/>
+    </row>
+    <row r="29" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>23</v>
       </c>
@@ -2591,10 +3104,28 @@
       <c r="S29" s="44">
         <v>0</v>
       </c>
-      <c r="T29" s="40"/>
-      <c r="V29" s="6"/>
-    </row>
-    <row r="30" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T29" s="44">
+        <v>0</v>
+      </c>
+      <c r="U29" s="44">
+        <v>0</v>
+      </c>
+      <c r="V29" s="44">
+        <v>0</v>
+      </c>
+      <c r="W29" s="44">
+        <v>0</v>
+      </c>
+      <c r="X29" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="40"/>
+      <c r="AB29" s="6"/>
+    </row>
+    <row r="30" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>6</v>
       </c>
@@ -2650,10 +3181,28 @@
       <c r="S30" s="44">
         <v>0</v>
       </c>
-      <c r="T30" s="40"/>
-      <c r="V30" s="6"/>
-    </row>
-    <row r="31" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T30" s="44">
+        <v>0</v>
+      </c>
+      <c r="U30" s="44">
+        <v>0</v>
+      </c>
+      <c r="V30" s="44">
+        <v>0</v>
+      </c>
+      <c r="W30" s="44">
+        <v>0</v>
+      </c>
+      <c r="X30" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="40"/>
+      <c r="AB30" s="6"/>
+    </row>
+    <row r="31" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>33</v>
       </c>
@@ -2709,10 +3258,28 @@
       <c r="S31" s="44">
         <v>0</v>
       </c>
-      <c r="T31" s="40"/>
-      <c r="V31" s="6"/>
-    </row>
-    <row r="32" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T31" s="44">
+        <v>0</v>
+      </c>
+      <c r="U31" s="44">
+        <v>0</v>
+      </c>
+      <c r="V31" s="44">
+        <v>0</v>
+      </c>
+      <c r="W31" s="44">
+        <v>0</v>
+      </c>
+      <c r="X31" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="40"/>
+      <c r="AB31" s="6"/>
+    </row>
+    <row r="32" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2768,10 +3335,28 @@
       <c r="S32" s="44">
         <v>0</v>
       </c>
-      <c r="T32" s="40"/>
-      <c r="V32" s="6"/>
-    </row>
-    <row r="33" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T32" s="44">
+        <v>0</v>
+      </c>
+      <c r="U32" s="44">
+        <v>0</v>
+      </c>
+      <c r="V32" s="44">
+        <v>0</v>
+      </c>
+      <c r="W32" s="44">
+        <v>0</v>
+      </c>
+      <c r="X32" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="40"/>
+      <c r="AB32" s="6"/>
+    </row>
+    <row r="33" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>36</v>
       </c>
@@ -2827,10 +3412,28 @@
       <c r="S33" s="44">
         <v>0</v>
       </c>
-      <c r="T33" s="40"/>
-      <c r="V33" s="6"/>
-    </row>
-    <row r="34" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T33" s="44">
+        <v>0</v>
+      </c>
+      <c r="U33" s="44">
+        <v>0</v>
+      </c>
+      <c r="V33" s="44">
+        <v>0</v>
+      </c>
+      <c r="W33" s="44">
+        <v>0</v>
+      </c>
+      <c r="X33" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="40"/>
+      <c r="AB33" s="6"/>
+    </row>
+    <row r="34" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>31</v>
       </c>
@@ -2886,10 +3489,28 @@
       <c r="S34" s="44">
         <v>0</v>
       </c>
-      <c r="T34" s="40"/>
-      <c r="V34" s="6"/>
-    </row>
-    <row r="35" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T34" s="44">
+        <v>0</v>
+      </c>
+      <c r="U34" s="44">
+        <v>0</v>
+      </c>
+      <c r="V34" s="44">
+        <v>0</v>
+      </c>
+      <c r="W34" s="44">
+        <v>0</v>
+      </c>
+      <c r="X34" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="40"/>
+      <c r="AB34" s="6"/>
+    </row>
+    <row r="35" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>72</v>
       </c>
@@ -2943,10 +3564,28 @@
       <c r="S35" s="44">
         <v>0</v>
       </c>
-      <c r="T35" s="40"/>
-      <c r="V35" s="6"/>
-    </row>
-    <row r="36" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T35" s="44">
+        <v>0</v>
+      </c>
+      <c r="U35" s="44">
+        <v>0</v>
+      </c>
+      <c r="V35" s="44">
+        <v>0</v>
+      </c>
+      <c r="W35" s="44">
+        <v>0</v>
+      </c>
+      <c r="X35" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="40"/>
+      <c r="AB35" s="6"/>
+    </row>
+    <row r="36" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>71</v>
       </c>
@@ -3000,10 +3639,28 @@
       <c r="S36" s="16">
         <v>0</v>
       </c>
-      <c r="T36" s="40"/>
-      <c r="V36" s="6"/>
-    </row>
-    <row r="37" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T36" s="44">
+        <v>0</v>
+      </c>
+      <c r="U36" s="44">
+        <v>0</v>
+      </c>
+      <c r="V36" s="44">
+        <v>0</v>
+      </c>
+      <c r="W36" s="44">
+        <v>0</v>
+      </c>
+      <c r="X36" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="40"/>
+      <c r="AB36" s="6"/>
+    </row>
+    <row r="37" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>40</v>
       </c>
@@ -3059,10 +3716,28 @@
       <c r="S37" s="44">
         <v>0</v>
       </c>
-      <c r="T37" s="40"/>
-      <c r="V37" s="6"/>
-    </row>
-    <row r="38" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T37" s="44">
+        <v>0</v>
+      </c>
+      <c r="U37" s="44">
+        <v>0</v>
+      </c>
+      <c r="V37" s="44">
+        <v>0</v>
+      </c>
+      <c r="W37" s="44">
+        <v>0</v>
+      </c>
+      <c r="X37" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="40"/>
+      <c r="AB37" s="6"/>
+    </row>
+    <row r="38" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>43</v>
       </c>
@@ -3118,10 +3793,28 @@
       <c r="S38" s="44">
         <v>0</v>
       </c>
-      <c r="T38" s="40"/>
-      <c r="V38" s="6"/>
-    </row>
-    <row r="39" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T38" s="44">
+        <v>0</v>
+      </c>
+      <c r="U38" s="44">
+        <v>0</v>
+      </c>
+      <c r="V38" s="44">
+        <v>0</v>
+      </c>
+      <c r="W38" s="44">
+        <v>0</v>
+      </c>
+      <c r="X38" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="40"/>
+      <c r="AB38" s="6"/>
+    </row>
+    <row r="39" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>44</v>
       </c>
@@ -3177,10 +3870,28 @@
       <c r="S39" s="44">
         <v>0</v>
       </c>
-      <c r="T39" s="40"/>
-      <c r="V39" s="6"/>
-    </row>
-    <row r="40" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T39" s="44">
+        <v>0</v>
+      </c>
+      <c r="U39" s="44">
+        <v>0</v>
+      </c>
+      <c r="V39" s="44">
+        <v>0</v>
+      </c>
+      <c r="W39" s="44">
+        <v>0</v>
+      </c>
+      <c r="X39" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="40"/>
+      <c r="AB39" s="6"/>
+    </row>
+    <row r="40" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
@@ -3236,10 +3947,28 @@
       <c r="S40" s="44">
         <v>0</v>
       </c>
-      <c r="T40" s="40"/>
-      <c r="V40" s="6"/>
-    </row>
-    <row r="41" spans="1:22" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T40" s="44">
+        <v>0</v>
+      </c>
+      <c r="U40" s="44">
+        <v>0</v>
+      </c>
+      <c r="V40" s="44">
+        <v>0</v>
+      </c>
+      <c r="W40" s="44">
+        <v>0</v>
+      </c>
+      <c r="X40" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="40"/>
+      <c r="AB40" s="6"/>
+    </row>
+    <row r="41" spans="1:28" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>46</v>
       </c>
@@ -3295,10 +4024,28 @@
       <c r="S41" s="44">
         <v>0</v>
       </c>
-      <c r="T41" s="40"/>
-      <c r="V41" s="6"/>
-    </row>
-    <row r="42" spans="1:22" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T41" s="44">
+        <v>0</v>
+      </c>
+      <c r="U41" s="44">
+        <v>0</v>
+      </c>
+      <c r="V41" s="44">
+        <v>0</v>
+      </c>
+      <c r="W41" s="44">
+        <v>0</v>
+      </c>
+      <c r="X41" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="40"/>
+      <c r="AB41" s="6"/>
+    </row>
+    <row r="42" spans="1:28" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -3348,9 +4095,27 @@
       <c r="S42" s="44">
         <v>0</v>
       </c>
-      <c r="T42" s="40"/>
-    </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T42" s="44">
+        <v>0</v>
+      </c>
+      <c r="U42" s="44">
+        <v>0</v>
+      </c>
+      <c r="V42" s="44">
+        <v>0</v>
+      </c>
+      <c r="W42" s="44">
+        <v>0</v>
+      </c>
+      <c r="X42" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="40"/>
+    </row>
+    <row r="43" spans="1:28" s="2" customFormat="1" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
         <v>15</v>
       </c>
@@ -3394,39 +4159,63 @@
         <v>20</v>
       </c>
       <c r="M43" s="30">
-        <f t="shared" ref="M43:R43" si="1">SUM(M17:M42)</f>
+        <f t="shared" ref="M43:Y43" si="3">SUM(M17:M42)</f>
         <v>20</v>
       </c>
       <c r="N43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="O43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="P43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="Q43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="R43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="S43" s="30">
-        <f>SUM(S17:S42)</f>
-        <v>0</v>
-      </c>
-      <c r="T43" s="43">
-        <f>SUM(D43:S43)</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="43">
+        <f>SUM(D43:Y43)</f>
         <v>830</v>
       </c>
     </row>
-    <row r="44" spans="1:22" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:28" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="8"/>
@@ -3476,9 +4265,27 @@
       <c r="S44" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T44" s="41"/>
-    </row>
-    <row r="45" spans="1:22" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z44" s="41"/>
+    </row>
+    <row r="45" spans="1:28" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="8"/>
@@ -3528,16 +4335,34 @@
       <c r="S45" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T45" s="41"/>
-    </row>
-    <row r="46" spans="1:22" s="2" customFormat="1" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y45" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z45" s="41"/>
+    </row>
+    <row r="46" spans="1:28" s="2" customFormat="1" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
-      <c r="C46" s="45" t="s">
+      <c r="C46" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="46"/>
-      <c r="E46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="48"/>
       <c r="F46" s="31"/>
       <c r="G46" s="15" t="s">
         <v>14</v>
@@ -3578,9 +4403,27 @@
       <c r="S46" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="T46" s="41"/>
-    </row>
-    <row r="47" spans="1:22" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="U46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="V46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="W46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="X46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y46" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z46" s="41"/>
+    </row>
+    <row r="47" spans="1:28" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>52</v>
       </c>
@@ -3636,9 +4479,27 @@
       <c r="S47" s="44">
         <v>0</v>
       </c>
-      <c r="T47" s="41"/>
-    </row>
-    <row r="48" spans="1:22" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T47" s="44">
+        <v>0</v>
+      </c>
+      <c r="U47" s="44">
+        <v>0</v>
+      </c>
+      <c r="V47" s="44">
+        <v>0</v>
+      </c>
+      <c r="W47" s="44">
+        <v>0</v>
+      </c>
+      <c r="X47" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="41"/>
+    </row>
+    <row r="48" spans="1:28" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>73</v>
       </c>
@@ -3694,9 +4555,27 @@
       <c r="S48" s="44">
         <v>0</v>
       </c>
-      <c r="T48" s="41"/>
-    </row>
-    <row r="49" spans="1:20" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T48" s="44">
+        <v>0</v>
+      </c>
+      <c r="U48" s="44">
+        <v>0</v>
+      </c>
+      <c r="V48" s="44">
+        <v>0</v>
+      </c>
+      <c r="W48" s="44">
+        <v>0</v>
+      </c>
+      <c r="X48" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="41"/>
+    </row>
+    <row r="49" spans="1:26" s="2" customFormat="1" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>53</v>
       </c>
@@ -3752,9 +4631,27 @@
       <c r="S49" s="44">
         <v>0</v>
       </c>
-      <c r="T49" s="41"/>
-    </row>
-    <row r="50" spans="1:20" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T49" s="44">
+        <v>0</v>
+      </c>
+      <c r="U49" s="44">
+        <v>0</v>
+      </c>
+      <c r="V49" s="44">
+        <v>0</v>
+      </c>
+      <c r="W49" s="44">
+        <v>0</v>
+      </c>
+      <c r="X49" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="41"/>
+    </row>
+    <row r="50" spans="1:26" ht="29" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="10" t="s">
         <v>17</v>
       </c>
@@ -3774,63 +4671,87 @@
         <v>-110</v>
       </c>
       <c r="G50" s="32">
-        <f>SUM(G47:G49)</f>
+        <f t="shared" ref="G50:M50" si="4">SUM(G47:G49)</f>
         <v>30</v>
       </c>
       <c r="H50" s="32">
-        <f>SUM(H47:H49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="I50" s="32">
-        <f>SUM(I47:I49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="J50" s="32">
-        <f>SUM(J47:J49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="K50" s="37">
-        <f>SUM(K47:K49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="L50" s="37">
-        <f>SUM(L47:L49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="M50" s="37">
-        <f>SUM(M47:M49)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="N50" s="37">
-        <f t="shared" ref="N50:R50" si="2">SUM(N47:N49)</f>
+        <f t="shared" ref="N50:R50" si="5">SUM(N47:N49)</f>
         <v>30</v>
       </c>
       <c r="O50" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="P50" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="Q50" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="R50" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S50" s="37">
         <f>SUM(S47:S49)</f>
         <v>0</v>
       </c>
-      <c r="T50" s="42">
-        <f>SUM(D50:S50)</f>
+      <c r="T50" s="37">
+        <f>SUM(T47:T49)</f>
+        <v>0</v>
+      </c>
+      <c r="U50" s="37">
+        <f t="shared" ref="U50:Y50" si="6">SUM(U47:U49)</f>
+        <v>0</v>
+      </c>
+      <c r="V50" s="37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z50" s="42">
+        <f>SUM(D50:Y50)</f>
         <v>580</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="23" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="23" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3850,8 +4771,14 @@
       <c r="Q51" s="22"/>
       <c r="R51" s="22"/>
       <c r="S51" s="22"/>
-    </row>
-    <row r="52" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T51" s="22"/>
+      <c r="U51" s="22"/>
+      <c r="V51" s="22"/>
+      <c r="W51" s="22"/>
+      <c r="X51" s="22"/>
+      <c r="Y51" s="22"/>
+    </row>
+    <row r="52" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3871,8 +4798,14 @@
       <c r="Q52" s="22"/>
       <c r="R52" s="22"/>
       <c r="S52" s="22"/>
-    </row>
-    <row r="53" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="22"/>
+      <c r="W52" s="22"/>
+      <c r="X52" s="22"/>
+      <c r="Y52" s="22"/>
+    </row>
+    <row r="53" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3892,8 +4825,14 @@
       <c r="Q53" s="22"/>
       <c r="R53" s="22"/>
       <c r="S53" s="22"/>
-    </row>
-    <row r="54" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="22"/>
+      <c r="W53" s="22"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="22"/>
+    </row>
+    <row r="54" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="J54" s="35"/>
       <c r="K54" s="35"/>
       <c r="L54" s="35"/>
@@ -3904,6 +4843,12 @@
       <c r="Q54" s="35"/>
       <c r="R54" s="35"/>
       <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="U54" s="35"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="35"/>
+      <c r="X54" s="35"/>
+      <c r="Y54" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/assets/Excells/CotisationSpeciale0.xlsx
+++ b/assets/Excells/CotisationSpeciale0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwamutalamiantezila/Documents/LukalaPhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE96D20-BA2C-8741-B50A-FD630FEF5086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97E7315-60EB-CC48-B46D-65E48E6A8026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1480" yWindow="680" windowWidth="34140" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
+    <workbookView xWindow="800" yWindow="5160" windowWidth="34140" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="74">
   <si>
     <t>Eugenie Malayi</t>
   </si>
@@ -258,9 +258,6 @@
   </si>
   <si>
     <t>René Mamingi</t>
-  </si>
-  <si>
-    <t>Juille</t>
   </si>
 </sst>
 </file>
@@ -983,7 +980,7 @@
         <v>59</v>
       </c>
       <c r="Y1" s="27" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="Z1" s="38"/>
     </row>

--- a/assets/Excells/CotisationSpeciale0.xlsx
+++ b/assets/Excells/CotisationSpeciale0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bwamutalamiantezila/Documents/LukalaPhoto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97E7315-60EB-CC48-B46D-65E48E6A8026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E97AC29-04E8-8843-82C1-D0373F802FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="5160" windowWidth="34140" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
+    <workbookView xWindow="3320" yWindow="2200" windowWidth="30240" windowHeight="16600" xr2:uid="{68E375EF-7E04-A04A-8B5D-972BEA3F72AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
